--- a/Raw Data/Micro Plans/November 2025/Micro Plan - TA-504 Nov'25.xlsx
+++ b/Raw Data/Micro Plans/November 2025/Micro Plan - TA-504 Nov'25.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\DPR\TA-504\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaushikb\Documents\Work\Git\Office-work-\Raw Data\Micro Plans\November 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7E8B09-0672-410F-968C-B8D654793003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B007D3-3883-4723-90B1-75F012618902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="757" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="757" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FDN-June25" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="Stub dispatch" sheetId="4" state="hidden" r:id="rId2"/>
     <sheet name="Erection-Nov25" sheetId="2" r:id="rId3"/>
-    <sheet name="Stringing- Nov25 " sheetId="6" r:id="rId4"/>
-    <sheet name="STG-Sep25" sheetId="3" state="hidden" r:id="rId5"/>
+    <sheet name="STG-Sep25" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Erection-Nov25'!$A$1:$O$22</definedName>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="151">
   <si>
     <t>Project Code</t>
   </si>
@@ -409,78 +408,6 @@
   </si>
   <si>
     <t>27/0</t>
-  </si>
-  <si>
-    <t>Name of the line : 765 KV D/C Bikaner III - Neemrana II TL02</t>
-  </si>
-  <si>
-    <t>Powergrid Bikaner Neemrana Transmission Limited (Power Grid Corporation of India)</t>
-  </si>
-  <si>
-    <t>Executing Agency:- KEC International Limited</t>
-  </si>
-  <si>
-    <t>Datewise Stringing planning for the month of November 2025</t>
-  </si>
-  <si>
-    <t>Sr no</t>
-  </si>
-  <si>
-    <t>Section Name</t>
-  </si>
-  <si>
-    <t>Tower Erection  Status</t>
-  </si>
-  <si>
-    <t>Tower in section</t>
-  </si>
-  <si>
-    <t>Insulator Hoisting</t>
-  </si>
-  <si>
-    <t>Paying Out Start</t>
-  </si>
-  <si>
-    <t>Paying Out Completed</t>
-  </si>
-  <si>
-    <t>Final sag complete</t>
-  </si>
-  <si>
-    <t>AP-6 - AP-7/0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete </t>
-  </si>
-  <si>
-    <t>Rahim Khan</t>
-  </si>
-  <si>
-    <t>AP-5 - AP-5A/0</t>
-  </si>
-  <si>
-    <t>AP-5A/0 - AP-6</t>
-  </si>
-  <si>
-    <t>AP-32A/0 - AP-33/0</t>
-  </si>
-  <si>
-    <t>Tanjira Bibi</t>
-  </si>
-  <si>
-    <t>AP-32/0 - AP-32A/0</t>
-  </si>
-  <si>
-    <t>AP-33/0 - AP-34/0</t>
-  </si>
-  <si>
-    <t>Total length (KM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Micro Plan - Stringing </t>
-  </si>
-  <si>
-    <t>Section Length Miter</t>
   </si>
   <si>
     <t>11/5</t>
@@ -578,17 +505,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="167" formatCode="[$-409]d/mmm/yy;@"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="#,##0.000"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
-    <numFmt numFmtId="171" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="167" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="168" formatCode="[$-409]d/mmm/yy;@"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="#,##0.000"/>
+    <numFmt numFmtId="171" formatCode="0.000"/>
+    <numFmt numFmtId="172" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -792,12 +719,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Verdana"/>
@@ -830,7 +751,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -896,14 +817,8 @@
         <fgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="30">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1106,205 +1021,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
@@ -1323,21 +1050,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -1357,13 +1084,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
@@ -1435,11 +1162,11 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -1482,36 +1209,36 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="226">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1555,13 +1282,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1570,25 +1297,25 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1597,31 +1324,31 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1630,13 +1357,13 @@
     <xf numFmtId="17" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1651,7 +1378,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -1666,41 +1393,41 @@
     <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="17" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="1" fontId="17" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="6" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="6" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1728,7 +1455,7 @@
     <xf numFmtId="1" fontId="20" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="8" borderId="3" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="18" fillId="8" borderId="3" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1741,7 +1468,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1765,16 +1492,16 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -1786,16 +1513,16 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1807,7 +1534,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1846,19 +1573,19 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1867,7 +1594,7 @@
     <xf numFmtId="2" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1876,7 +1603,7 @@
     <xf numFmtId="2" fontId="26" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1915,10 +1642,10 @@
     <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="23" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1948,92 +1675,84 @@
     <xf numFmtId="14" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="12" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="28" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="28" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="14" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="33" fillId="0" borderId="7" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2049,51 +1768,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2109,74 +1783,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="20" xfId="78" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="1" xfId="78" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="19" xfId="78" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="16" xfId="78" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="28" xfId="78" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="18" xfId="78" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="34" fillId="0" borderId="7" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="172">
@@ -2356,68 +1973,8 @@
   <dxfs count="70">
     <dxf>
       <font>
-        <color indexed="20"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="45"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="20"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="45"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="20"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="45"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="20"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="45"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2486,6 +2043,66 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="20"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="45"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="20"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="45"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="20"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="45"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="20"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="45"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2741,6 +2358,16 @@
     </dxf>
     <dxf>
       <font>
+        <color indexed="17"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="42"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color indexed="20"/>
       </font>
       <fill>
@@ -2763,16 +2390,6 @@
       <font>
         <color indexed="20"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="17"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="42"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3594,137 +3211,137 @@
       <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:33" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="180" t="s">
+      <c r="A18" s="176" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="180" t="s">
+      <c r="B18" s="176" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="177" t="s">
+      <c r="C18" s="172" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="180" t="s">
+      <c r="D18" s="176" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="177" t="s">
+      <c r="E18" s="172" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="177" t="s">
+      <c r="F18" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="180" t="s">
+      <c r="G18" s="176" t="s">
         <v>8</v>
       </c>
-      <c r="H18" s="192" t="s">
+      <c r="H18" s="163" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="192"/>
-      <c r="J18" s="192"/>
-      <c r="K18" s="192"/>
-      <c r="L18" s="192"/>
-      <c r="M18" s="192"/>
-      <c r="N18" s="192"/>
-      <c r="O18" s="192"/>
-      <c r="P18" s="185" t="s">
+      <c r="I18" s="163"/>
+      <c r="J18" s="163"/>
+      <c r="K18" s="163"/>
+      <c r="L18" s="163"/>
+      <c r="M18" s="163"/>
+      <c r="N18" s="163"/>
+      <c r="O18" s="163"/>
+      <c r="P18" s="166" t="s">
         <v>19</v>
       </c>
-      <c r="R18" s="177" t="s">
+      <c r="R18" s="172" t="s">
         <v>36</v>
       </c>
-      <c r="T18" s="186" t="s">
+      <c r="T18" s="167" t="s">
         <v>31</v>
       </c>
-      <c r="U18" s="187"/>
-      <c r="V18" s="187"/>
-      <c r="W18" s="187"/>
-      <c r="X18" s="187"/>
-      <c r="Y18" s="188"/>
-      <c r="AA18" s="186" t="s">
+      <c r="U18" s="168"/>
+      <c r="V18" s="168"/>
+      <c r="W18" s="168"/>
+      <c r="X18" s="168"/>
+      <c r="Y18" s="169"/>
+      <c r="AA18" s="167" t="s">
         <v>30</v>
       </c>
-      <c r="AB18" s="187"/>
-      <c r="AC18" s="187"/>
-      <c r="AD18" s="187"/>
-      <c r="AE18" s="187"/>
-      <c r="AF18" s="188"/>
-      <c r="AG18" s="189" t="s">
+      <c r="AB18" s="168"/>
+      <c r="AC18" s="168"/>
+      <c r="AD18" s="168"/>
+      <c r="AE18" s="168"/>
+      <c r="AF18" s="169"/>
+      <c r="AG18" s="170" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="181"/>
-      <c r="B19" s="181"/>
-      <c r="C19" s="178"/>
-      <c r="D19" s="181"/>
-      <c r="E19" s="178"/>
-      <c r="F19" s="178"/>
-      <c r="G19" s="181"/>
-      <c r="H19" s="197" t="s">
+      <c r="A19" s="177"/>
+      <c r="B19" s="177"/>
+      <c r="C19" s="174"/>
+      <c r="D19" s="177"/>
+      <c r="E19" s="174"/>
+      <c r="F19" s="174"/>
+      <c r="G19" s="177"/>
+      <c r="H19" s="162" t="s">
         <v>9</v>
       </c>
-      <c r="I19" s="197"/>
-      <c r="J19" s="197" t="s">
+      <c r="I19" s="162"/>
+      <c r="J19" s="162" t="s">
         <v>12</v>
       </c>
-      <c r="K19" s="197"/>
-      <c r="L19" s="197" t="s">
+      <c r="K19" s="162"/>
+      <c r="L19" s="162" t="s">
         <v>13</v>
       </c>
-      <c r="M19" s="197"/>
-      <c r="N19" s="193" t="s">
+      <c r="M19" s="162"/>
+      <c r="N19" s="160" t="s">
         <v>15</v>
       </c>
-      <c r="O19" s="193" t="s">
+      <c r="O19" s="160" t="s">
         <v>14</v>
       </c>
-      <c r="P19" s="185"/>
-      <c r="R19" s="191"/>
-      <c r="T19" s="183" t="s">
+      <c r="P19" s="166"/>
+      <c r="R19" s="173"/>
+      <c r="T19" s="164" t="s">
         <v>24</v>
       </c>
-      <c r="U19" s="183" t="s">
+      <c r="U19" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="V19" s="183" t="s">
+      <c r="V19" s="164" t="s">
         <v>26</v>
       </c>
-      <c r="W19" s="183" t="s">
+      <c r="W19" s="164" t="s">
         <v>27</v>
       </c>
-      <c r="X19" s="183" t="s">
+      <c r="X19" s="164" t="s">
         <v>28</v>
       </c>
       <c r="Y19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AA19" s="183" t="s">
+      <c r="AA19" s="164" t="s">
         <v>24</v>
       </c>
-      <c r="AB19" s="183" t="s">
+      <c r="AB19" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="AC19" s="183" t="s">
+      <c r="AC19" s="164" t="s">
         <v>26</v>
       </c>
-      <c r="AD19" s="183" t="s">
+      <c r="AD19" s="164" t="s">
         <v>27</v>
       </c>
-      <c r="AE19" s="183" t="s">
+      <c r="AE19" s="164" t="s">
         <v>28</v>
       </c>
       <c r="AF19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AG19" s="190"/>
+      <c r="AG19" s="171"/>
     </row>
     <row r="20" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="182"/>
-      <c r="B20" s="181"/>
-      <c r="C20" s="178"/>
-      <c r="D20" s="181"/>
-      <c r="E20" s="179"/>
-      <c r="F20" s="179"/>
-      <c r="G20" s="181"/>
+      <c r="A20" s="178"/>
+      <c r="B20" s="177"/>
+      <c r="C20" s="174"/>
+      <c r="D20" s="177"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="175"/>
+      <c r="G20" s="177"/>
       <c r="H20" s="93" t="s">
         <v>10</v>
       </c>
@@ -3743,25 +3360,25 @@
       <c r="M20" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="N20" s="194"/>
-      <c r="O20" s="194"/>
+      <c r="N20" s="161"/>
+      <c r="O20" s="161"/>
       <c r="P20" s="44" t="s">
         <v>50</v>
       </c>
       <c r="R20" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="T20" s="184"/>
-      <c r="U20" s="184"/>
-      <c r="V20" s="184"/>
-      <c r="W20" s="184"/>
-      <c r="X20" s="184"/>
+      <c r="T20" s="165"/>
+      <c r="U20" s="165"/>
+      <c r="V20" s="165"/>
+      <c r="W20" s="165"/>
+      <c r="X20" s="165"/>
       <c r="Y20" s="19"/>
-      <c r="AA20" s="184"/>
-      <c r="AB20" s="184"/>
-      <c r="AC20" s="184"/>
-      <c r="AD20" s="184"/>
-      <c r="AE20" s="184"/>
+      <c r="AA20" s="165"/>
+      <c r="AB20" s="165"/>
+      <c r="AC20" s="165"/>
+      <c r="AD20" s="165"/>
+      <c r="AE20" s="165"/>
       <c r="AF20" s="19" t="s">
         <v>50</v>
       </c>
@@ -4032,7 +3649,7 @@
       <c r="D25" s="85"/>
       <c r="E25" s="100"/>
       <c r="F25" s="8"/>
-      <c r="G25" s="195"/>
+      <c r="G25" s="158"/>
       <c r="H25" s="98"/>
       <c r="I25" s="98"/>
       <c r="J25" s="98"/>
@@ -4090,7 +3707,7 @@
       <c r="D26" s="8"/>
       <c r="E26" s="101"/>
       <c r="F26" s="96"/>
-      <c r="G26" s="196"/>
+      <c r="G26" s="159"/>
       <c r="H26" s="98"/>
       <c r="I26" s="98"/>
       <c r="J26" s="98"/>
@@ -4445,16 +4062,13 @@
     <filterColumn colId="13" showButton="0"/>
   </autoFilter>
   <mergeCells count="29">
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="O19:O20"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="H18:O18"/>
-    <mergeCell ref="N19:N20"/>
-    <mergeCell ref="U19:U20"/>
-    <mergeCell ref="V19:V20"/>
-    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
     <mergeCell ref="X19:X20"/>
     <mergeCell ref="P18:P19"/>
     <mergeCell ref="AA18:AF18"/>
@@ -4467,13 +4081,16 @@
     <mergeCell ref="R18:R19"/>
     <mergeCell ref="T18:Y18"/>
     <mergeCell ref="T19:T20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="H18:O18"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="U19:U20"/>
+    <mergeCell ref="V19:V20"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:M19"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="B21">
@@ -4548,17 +4165,17 @@
     <cfRule type="expression" dxfId="43" priority="1243" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$123, B26)+COUNTIF($D$142:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="1244" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="1245" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B26)+COUNTIF($D$214:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="1245" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="1246" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B26)+COUNTIF($D$214:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="1246" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="1247" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$474:$D$65380, B26)+COUNTIF($D$454:$D$455, B26)+COUNTIF($D$416:$D$417, B26)+COUNTIF($D$374:$D$377, B26)+COUNTIF($D$351:$D$352, B26)+COUNTIF($D$324:$D$325, B26)+COUNTIF($D$303:$D$303, B26)+COUNTIF($D$288:$D$289, B26)+COUNTIF($D$263:$D$263, B26)+COUNTIF($D$252:$D$253, B26)+COUNTIF($D$233:$D$234, B26)+COUNTIF($D$51:$D$218, B26)+COUNTIF($D$219:$D$220, B26)+COUNTIF($D$1:$D$50, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="1244" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B26)+COUNTIF($D$214:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="39" priority="1247" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$474:$D$65380, B26)+COUNTIF($D$454:$D$455, B26)+COUNTIF($D$416:$D$417, B26)+COUNTIF($D$374:$D$377, B26)+COUNTIF($D$351:$D$352, B26)+COUNTIF($D$324:$D$325, B26)+COUNTIF($D$303:$D$303, B26)+COUNTIF($D$288:$D$289, B26)+COUNTIF($D$263:$D$263, B26)+COUNTIF($D$252:$D$253, B26)+COUNTIF($D$233:$D$234, B26)+COUNTIF($D$51:$D$218, B26)+COUNTIF($D$219:$D$220, B26)+COUNTIF($D$1:$D$50, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
@@ -4575,55 +4192,55 @@
     <cfRule type="duplicateValues" dxfId="32" priority="347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4">
-    <cfRule type="expression" dxfId="31" priority="1220" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="1221" stopIfTrue="1">
+      <formula>AND(COUNTIF($C$1:$C$65460, L4)+COUNTIF(#REF!, L4)&gt;1,NOT(ISBLANK(L4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="1220" stopIfTrue="1">
       <formula>AND(COUNTIF($C$314:$C$65460, L4)+COUNTIF($C$294:$C$295, L4)+COUNTIF($C$256:$C$257, L4)+COUNTIF($C$214:$C$217, L4)+COUNTIF($C$191:$C$192, L4)+COUNTIF($C$164:$C$165, L4)+COUNTIF($C$143:$C$143, L4)+COUNTIF($C$128:$C$129, L4)+COUNTIF($C$103:$C$103, L4)+COUNTIF($C$92:$C$93, L4)+COUNTIF($C$73:$C$74, L4)+COUNTIF($C$29:$C$56, L4)+COUNTIF($C$58:$C$60, L4)+COUNTIF($C$1:$C$27, L4)&gt;1,NOT(ISBLANK(L4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="1221" stopIfTrue="1">
-      <formula>AND(COUNTIF($C$1:$C$65460, L4)+COUNTIF(#REF!, L4)&gt;1,NOT(ISBLANK(L4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4">
-    <cfRule type="expression" dxfId="29" priority="1222" stopIfTrue="1">
-      <formula>AND(COUNTIF($D$331:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$314:$D$315, M4)+COUNTIF($D$294:$D$295, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="1223" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="1223" stopIfTrue="1">
       <formula>AND(COUNTIF($D$314:$D$65460, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$294:$D$295, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="1224" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="1224" stopIfTrue="1">
       <formula>AND(COUNTIF($D$294:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="1225" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="1225" stopIfTrue="1">
       <formula>AND(COUNTIF($D$256:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="1226" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="1226" stopIfTrue="1">
       <formula>AND(COUNTIF($D$214:$D$65460, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="1227" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="1227" stopIfTrue="1">
       <formula>AND(COUNTIF($D$214:$D$65460, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$51:$D$51, M4)+COUNTIF($D$53:$D$60, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="1228" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="1228" stopIfTrue="1">
       <formula>AND(COUNTIF($D$191:$D$65460, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$51:$D$51, M4)+COUNTIF($D$53:$D$60, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="1229" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="1229" stopIfTrue="1">
       <formula>AND(COUNTIF($F$369:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$352:$F$353, M4)+COUNTIF($F$332:$F$333, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="1230" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="1230" stopIfTrue="1">
       <formula>AND(COUNTIF($F$352:$F$65454, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$332:$F$333, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="1231" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="1231" stopIfTrue="1">
       <formula>AND(COUNTIF($F$332:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="1232" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="1232" stopIfTrue="1">
       <formula>AND(COUNTIF($F$294:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="1233" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="1233" stopIfTrue="1">
       <formula>AND(COUNTIF($F$252:$F$65454, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="1234" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="1234" stopIfTrue="1">
       <formula>AND(COUNTIF($F$252:$F$65454, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$89:$F$89, M4)+COUNTIF($F$91:$F$98, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="1235" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="1235" stopIfTrue="1">
       <formula>AND(COUNTIF($F$229:$F$65454, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$89:$F$89, M4)+COUNTIF($F$91:$F$98, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="1222" stopIfTrue="1">
+      <formula>AND(COUNTIF($D$331:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$314:$D$315, M4)+COUNTIF($D$294:$D$295, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -4744,7 +4361,7 @@
       <c r="Q4" s="70">
         <v>0</v>
       </c>
-      <c r="R4" s="198" t="s">
+      <c r="R4" s="179" t="s">
         <v>75</v>
       </c>
     </row>
@@ -4787,14 +4404,14 @@
       <c r="Q5" s="70">
         <v>0</v>
       </c>
-      <c r="R5" s="199"/>
+      <c r="R5" s="180"/>
     </row>
     <row r="6" spans="2:18" s="75" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="200" t="s">
+      <c r="B6" s="181" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="201"/>
-      <c r="D6" s="202"/>
+      <c r="C6" s="182"/>
+      <c r="D6" s="183"/>
       <c r="E6" s="73">
         <v>160</v>
       </c>
@@ -4922,22 +4539,22 @@
       <c r="A2" s="135">
         <v>1</v>
       </c>
-      <c r="B2" s="223" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="223" t="s">
-        <v>146</v>
-      </c>
-      <c r="D2" s="224">
+      <c r="B2" s="155" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="155" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="156">
         <v>37.931087999999995</v>
       </c>
       <c r="E2" s="153"/>
       <c r="F2" s="136"/>
       <c r="G2" s="137" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="H2" s="152" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="I2" s="137"/>
       <c r="J2" s="138"/>
@@ -4955,22 +4572,22 @@
       <c r="A3" s="135">
         <v>2</v>
       </c>
-      <c r="B3" s="223" t="s">
+      <c r="B3" s="155" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="223" t="s">
-        <v>147</v>
-      </c>
-      <c r="D3" s="224">
+      <c r="C3" s="155" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" s="156">
         <v>59.500628000000006</v>
       </c>
       <c r="E3" s="153"/>
       <c r="F3" s="136"/>
       <c r="G3" s="137" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="H3" s="152" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="I3" s="137"/>
       <c r="J3" s="138"/>
@@ -5004,22 +4621,22 @@
       <c r="A4" s="135">
         <v>3</v>
       </c>
-      <c r="B4" s="223" t="s">
+      <c r="B4" s="155" t="s">
         <v>118</v>
       </c>
-      <c r="C4" s="223" t="s">
-        <v>148</v>
-      </c>
-      <c r="D4" s="224">
+      <c r="C4" s="155" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" s="156">
         <v>73.244547999999995</v>
       </c>
       <c r="E4" s="153"/>
       <c r="F4" s="136"/>
       <c r="G4" s="137" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="H4" s="152" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="I4" s="137"/>
       <c r="J4" s="138"/>
@@ -5053,22 +4670,22 @@
       <c r="A5" s="135">
         <v>4</v>
       </c>
-      <c r="B5" s="223" t="s">
-        <v>149</v>
-      </c>
-      <c r="C5" s="223" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="224">
+      <c r="B5" s="155" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="155" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="156">
         <v>36.159756000000002</v>
       </c>
       <c r="E5" s="153"/>
       <c r="F5" s="136"/>
       <c r="G5" s="137" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="H5" s="152" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="I5" s="137"/>
       <c r="J5" s="138"/>
@@ -5102,22 +4719,22 @@
       <c r="A6" s="135">
         <v>5</v>
       </c>
-      <c r="B6" s="223" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" s="223" t="s">
-        <v>152</v>
-      </c>
-      <c r="D6" s="224">
+      <c r="B6" s="155" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="155" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="156">
         <v>45.697021999999997</v>
       </c>
       <c r="E6" s="153"/>
       <c r="F6" s="136"/>
       <c r="G6" s="137" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="H6" s="152" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="I6" s="137"/>
       <c r="J6" s="138"/>
@@ -5151,22 +4768,22 @@
       <c r="A7" s="135">
         <v>6</v>
       </c>
-      <c r="B7" s="223" t="s">
+      <c r="B7" s="155" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="223" t="s">
-        <v>148</v>
-      </c>
-      <c r="D7" s="224">
+      <c r="C7" s="155" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="156">
         <v>73.244547999999995</v>
       </c>
       <c r="E7" s="153"/>
       <c r="F7" s="136"/>
       <c r="G7" s="137" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="H7" s="152" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="I7" s="137"/>
       <c r="J7" s="138"/>
@@ -5200,22 +4817,22 @@
       <c r="A8" s="135">
         <v>7</v>
       </c>
-      <c r="B8" s="223" t="s">
-        <v>153</v>
-      </c>
-      <c r="C8" s="223" t="s">
-        <v>152</v>
-      </c>
-      <c r="D8" s="224">
+      <c r="B8" s="155" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" s="155" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="156">
         <v>45.697021999999997</v>
       </c>
       <c r="E8" s="153"/>
       <c r="F8" s="136"/>
       <c r="G8" s="137" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="H8" s="152" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="I8" s="137"/>
       <c r="J8" s="138"/>
@@ -5249,22 +4866,22 @@
       <c r="A9" s="135">
         <v>8</v>
       </c>
-      <c r="B9" s="223" t="s">
-        <v>154</v>
-      </c>
-      <c r="C9" s="223" t="s">
-        <v>146</v>
-      </c>
-      <c r="D9" s="224">
+      <c r="B9" s="155" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="155" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="156">
         <v>37.931087999999995</v>
       </c>
       <c r="E9" s="153"/>
       <c r="F9" s="136"/>
       <c r="G9" s="137" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="H9" s="152" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="I9" s="137"/>
       <c r="J9" s="138"/>
@@ -5298,22 +4915,22 @@
       <c r="A10" s="135">
         <v>9</v>
       </c>
-      <c r="B10" s="223" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="223" t="s">
-        <v>156</v>
-      </c>
-      <c r="D10" s="224">
+      <c r="B10" s="155" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="155" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="156">
         <v>70.744719999999987</v>
       </c>
       <c r="E10" s="153"/>
       <c r="F10" s="136"/>
       <c r="G10" s="137" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="H10" s="152" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="I10" s="137"/>
       <c r="J10" s="138"/>
@@ -5348,22 +4965,22 @@
       <c r="A11" s="135">
         <v>10</v>
       </c>
-      <c r="B11" s="223" t="s">
+      <c r="B11" s="155" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="223" t="s">
-        <v>157</v>
-      </c>
-      <c r="D11" s="224">
+      <c r="C11" s="155" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" s="156">
         <v>67.261728000000005</v>
       </c>
       <c r="E11" s="153"/>
       <c r="F11" s="136"/>
       <c r="G11" s="137" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="H11" s="152" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="I11" s="137"/>
       <c r="J11" s="138"/>
@@ -5397,22 +5014,22 @@
       <c r="A12" s="135">
         <v>11</v>
       </c>
-      <c r="B12" s="223" t="s">
-        <v>158</v>
-      </c>
-      <c r="C12" s="223" t="s">
-        <v>150</v>
-      </c>
-      <c r="D12" s="224">
+      <c r="B12" s="155" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" s="155" t="s">
+        <v>126</v>
+      </c>
+      <c r="D12" s="156">
         <v>36.159756000000002</v>
       </c>
       <c r="E12" s="153"/>
       <c r="F12" s="136"/>
       <c r="G12" s="137" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="H12" s="152" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="I12" s="137"/>
       <c r="J12" s="138"/>
@@ -5446,22 +5063,22 @@
       <c r="A13" s="135">
         <v>12</v>
       </c>
-      <c r="B13" s="223" t="s">
-        <v>159</v>
-      </c>
-      <c r="C13" s="223" t="s">
-        <v>150</v>
-      </c>
-      <c r="D13" s="224">
+      <c r="B13" s="155" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="155" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="156">
         <v>36.159756000000002</v>
       </c>
       <c r="E13" s="153"/>
       <c r="F13" s="136"/>
       <c r="G13" s="137" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="H13" s="152" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="I13" s="137"/>
       <c r="J13" s="138"/>
@@ -5495,22 +5112,22 @@
       <c r="A14" s="135">
         <v>13</v>
       </c>
-      <c r="B14" s="223" t="s">
+      <c r="B14" s="155" t="s">
         <v>120</v>
       </c>
-      <c r="C14" s="223" t="s">
-        <v>160</v>
-      </c>
-      <c r="D14" s="224">
+      <c r="C14" s="155" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" s="156">
         <v>62.443705999999999</v>
       </c>
       <c r="E14" s="153"/>
       <c r="F14" s="136"/>
       <c r="G14" s="137" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="H14" s="152" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="I14" s="137"/>
       <c r="J14" s="138"/>
@@ -5544,22 +5161,22 @@
       <c r="A15" s="135">
         <v>14</v>
       </c>
-      <c r="B15" s="223" t="s">
+      <c r="B15" s="155" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="223" t="s">
-        <v>160</v>
-      </c>
-      <c r="D15" s="224">
+      <c r="C15" s="155" t="s">
+        <v>136</v>
+      </c>
+      <c r="D15" s="156">
         <v>62.443705999999999</v>
       </c>
       <c r="E15" s="153"/>
       <c r="F15" s="136"/>
       <c r="G15" s="137" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="H15" s="152" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="I15" s="137"/>
       <c r="J15" s="138"/>
@@ -5593,22 +5210,22 @@
       <c r="A16" s="135">
         <v>15</v>
       </c>
-      <c r="B16" s="223" t="s">
-        <v>161</v>
-      </c>
-      <c r="C16" s="223" t="s">
-        <v>157</v>
-      </c>
-      <c r="D16" s="224">
+      <c r="B16" s="155" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="155" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="156">
         <v>67.261728000000005</v>
       </c>
       <c r="E16" s="153"/>
       <c r="F16" s="136"/>
       <c r="G16" s="137" t="s">
-        <v>171</v>
-      </c>
-      <c r="H16" s="225" t="s">
-        <v>174</v>
+        <v>147</v>
+      </c>
+      <c r="H16" s="157" t="s">
+        <v>150</v>
       </c>
       <c r="I16" s="137"/>
       <c r="J16" s="138"/>
@@ -5642,22 +5259,22 @@
       <c r="A17" s="135">
         <v>16</v>
       </c>
-      <c r="B17" s="223" t="s">
-        <v>162</v>
-      </c>
-      <c r="C17" s="223" t="s">
-        <v>152</v>
-      </c>
-      <c r="D17" s="224">
+      <c r="B17" s="155" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" s="155" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="156">
         <v>45.697021999999997</v>
       </c>
       <c r="E17" s="153"/>
       <c r="F17" s="136"/>
       <c r="G17" s="137" t="s">
-        <v>171</v>
-      </c>
-      <c r="H17" s="225" t="s">
-        <v>174</v>
+        <v>147</v>
+      </c>
+      <c r="H17" s="157" t="s">
+        <v>150</v>
       </c>
       <c r="I17" s="137"/>
       <c r="J17" s="138"/>
@@ -5691,22 +5308,22 @@
       <c r="A18" s="135">
         <v>17</v>
       </c>
-      <c r="B18" s="223" t="s">
-        <v>163</v>
-      </c>
-      <c r="C18" s="223" t="s">
-        <v>148</v>
-      </c>
-      <c r="D18" s="224">
+      <c r="B18" s="155" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" s="155" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" s="156">
         <v>73.244547999999995</v>
       </c>
       <c r="E18" s="153"/>
       <c r="F18" s="136"/>
       <c r="G18" s="137" t="s">
-        <v>171</v>
-      </c>
-      <c r="H18" s="225" t="s">
-        <v>174</v>
+        <v>147</v>
+      </c>
+      <c r="H18" s="157" t="s">
+        <v>150</v>
       </c>
       <c r="I18" s="137"/>
       <c r="J18" s="138"/>
@@ -5740,22 +5357,22 @@
       <c r="A19" s="135">
         <v>18</v>
       </c>
-      <c r="B19" s="223" t="s">
-        <v>164</v>
-      </c>
-      <c r="C19" s="223" t="s">
-        <v>165</v>
-      </c>
-      <c r="D19" s="224">
+      <c r="B19" s="155" t="s">
+        <v>140</v>
+      </c>
+      <c r="C19" s="155" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19" s="156">
         <v>65.022578999999993</v>
       </c>
       <c r="E19" s="153"/>
       <c r="F19" s="136"/>
       <c r="G19" s="137" t="s">
-        <v>171</v>
-      </c>
-      <c r="H19" s="225" t="s">
-        <v>174</v>
+        <v>147</v>
+      </c>
+      <c r="H19" s="157" t="s">
+        <v>150</v>
       </c>
       <c r="I19" s="137"/>
       <c r="J19" s="138"/>
@@ -5789,22 +5406,22 @@
       <c r="A20" s="135">
         <v>19</v>
       </c>
-      <c r="B20" s="223" t="s">
-        <v>166</v>
-      </c>
-      <c r="C20" s="223" t="s">
-        <v>167</v>
-      </c>
-      <c r="D20" s="224">
+      <c r="B20" s="155" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="155" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="156">
         <v>55.450851000000007</v>
       </c>
       <c r="E20" s="153"/>
       <c r="F20" s="136"/>
       <c r="G20" s="137" t="s">
-        <v>171</v>
-      </c>
-      <c r="H20" s="225" t="s">
-        <v>174</v>
+        <v>147</v>
+      </c>
+      <c r="H20" s="157" t="s">
+        <v>150</v>
       </c>
       <c r="I20" s="137"/>
       <c r="J20" s="138"/>
@@ -5837,22 +5454,22 @@
       <c r="A21" s="135">
         <v>20</v>
       </c>
-      <c r="B21" s="223" t="s">
-        <v>168</v>
-      </c>
-      <c r="C21" s="223" t="s">
-        <v>169</v>
-      </c>
-      <c r="D21" s="224">
+      <c r="B21" s="155" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="155" t="s">
+        <v>145</v>
+      </c>
+      <c r="D21" s="156">
         <v>66.775700999999998</v>
       </c>
       <c r="E21" s="153"/>
       <c r="F21" s="136"/>
       <c r="G21" s="137" t="s">
-        <v>171</v>
-      </c>
-      <c r="H21" s="225" t="s">
-        <v>174</v>
+        <v>147</v>
+      </c>
+      <c r="H21" s="157" t="s">
+        <v>150</v>
       </c>
       <c r="I21" s="137"/>
       <c r="J21" s="138"/>
@@ -5886,22 +5503,22 @@
       <c r="A22" s="135">
         <v>21</v>
       </c>
-      <c r="B22" s="223" t="s">
-        <v>170</v>
-      </c>
-      <c r="C22" s="223" t="s">
-        <v>157</v>
-      </c>
-      <c r="D22" s="224">
+      <c r="B22" s="155" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" s="155" t="s">
+        <v>133</v>
+      </c>
+      <c r="D22" s="156">
         <v>67.261728000000005</v>
       </c>
       <c r="E22" s="153"/>
       <c r="F22" s="136"/>
       <c r="G22" s="137" t="s">
-        <v>171</v>
-      </c>
-      <c r="H22" s="225" t="s">
-        <v>174</v>
+        <v>147</v>
+      </c>
+      <c r="H22" s="157" t="s">
+        <v>150</v>
       </c>
       <c r="I22" s="137"/>
       <c r="J22" s="138"/>
@@ -5933,56 +5550,52 @@
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="B2:B22">
+    <cfRule type="duplicateValues" dxfId="14" priority="5" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="6" stopIfTrue="1"/>
+    <cfRule type="expression" dxfId="12" priority="1343" stopIfTrue="1">
+      <formula>AND(COUNTIF(#REF!, B2)+COUNTIF($B$1:$B$22, B2)&gt;1,NOT(ISBLANK(B2)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="1344" stopIfTrue="1">
+      <formula>AND(COUNTIF($B$1:$B$22, B2)+COUNTIF($B$23:$B$65484, B2)&gt;1,NOT(ISBLANK(B2)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="1345" stopIfTrue="1">
+      <formula>AND(COUNTIF(#REF!, B2)+COUNTIF($B$1:$B$20, B2)+COUNTIF(#REF!, B2)&gt;1,NOT(ISBLANK(B2)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="1346" stopIfTrue="1">
+      <formula>AND(COUNTIF($B$1:$B$20, B2)+COUNTIF($B$23:$B$65484, B2)+COUNTIF(#REF!, B2)&gt;1,NOT(ISBLANK(B2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J2:J22 M2:N22">
-    <cfRule type="containsText" dxfId="14" priority="83" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="8" priority="83" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J22">
-    <cfRule type="containsText" dxfId="13" priority="56" operator="containsText" text="WIP">
+    <cfRule type="containsText" dxfId="7" priority="56" operator="containsText" text="WIP">
       <formula>NOT(ISERROR(SEARCH("WIP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="61" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="6" priority="61" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="62" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="5" priority="62" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N22 J2:J22">
-    <cfRule type="containsText" dxfId="10" priority="82" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="4" priority="82" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N22">
-    <cfRule type="containsText" dxfId="9" priority="80" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="3" priority="80" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",M2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="81" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="2" priority="81" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",M2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="172" operator="containsText" text="WIP">
+    <cfRule type="containsText" dxfId="1" priority="172" operator="containsText" text="WIP">
       <formula>NOT(ISERROR(SEARCH("WIP",M2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B22">
-    <cfRule type="duplicateValues" dxfId="6" priority="5" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="6" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B22">
-    <cfRule type="expression" dxfId="3" priority="1343" stopIfTrue="1">
-      <formula>AND(COUNTIF(#REF!, B2)+COUNTIF($B$1:$B$22, B2)&gt;1,NOT(ISBLANK(B2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="1344" stopIfTrue="1">
-      <formula>AND(COUNTIF($B$1:$B$22, B2)+COUNTIF($B$23:$B$65484, B2)&gt;1,NOT(ISBLANK(B2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="1345" stopIfTrue="1">
-      <formula>AND(COUNTIF(#REF!, B2)+COUNTIF($B$1:$B$20, B2)+COUNTIF(#REF!, B2)&gt;1,NOT(ISBLANK(B2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B22">
-    <cfRule type="expression" dxfId="0" priority="1346" stopIfTrue="1">
-      <formula>AND(COUNTIF($B$1:$B$20, B2)+COUNTIF($B$23:$B$65484, B2)+COUNTIF(#REF!, B2)&gt;1,NOT(ISBLANK(B2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -5992,382 +5605,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E3F0E1F-80A5-4555-9FE1-744B1DEBC4EC}">
-  <dimension ref="B1:L15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="1.26953125" customWidth="1"/>
-    <col min="3" max="3" width="20.81640625" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" customWidth="1"/>
-    <col min="5" max="5" width="14.54296875" customWidth="1"/>
-    <col min="6" max="6" width="11.1796875" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" customWidth="1"/>
-    <col min="8" max="8" width="12.54296875" customWidth="1"/>
-    <col min="9" max="9" width="15.1796875" customWidth="1"/>
-    <col min="10" max="10" width="11.1796875" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B1" s="215" t="s">
-        <v>121</v>
-      </c>
-      <c r="C1" s="215"/>
-      <c r="D1" s="215"/>
-      <c r="E1" s="215"/>
-      <c r="F1" s="215"/>
-      <c r="G1" s="215"/>
-      <c r="H1" s="215"/>
-      <c r="I1" s="215"/>
-      <c r="J1" s="215"/>
-      <c r="K1" s="215"/>
-      <c r="L1" s="215"/>
-    </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="216" t="s">
-        <v>122</v>
-      </c>
-      <c r="C2" s="216"/>
-      <c r="D2" s="216"/>
-      <c r="E2" s="216"/>
-      <c r="F2" s="216"/>
-      <c r="G2" s="216"/>
-      <c r="H2" s="216"/>
-      <c r="I2" s="216"/>
-      <c r="J2" s="216"/>
-      <c r="K2" s="216"/>
-      <c r="L2" s="216"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B3" s="217" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="217"/>
-      <c r="D3" s="217"/>
-      <c r="E3" s="217"/>
-      <c r="F3" s="217"/>
-      <c r="G3" s="217"/>
-      <c r="H3" s="217"/>
-      <c r="I3" s="217"/>
-      <c r="J3" s="217"/>
-      <c r="K3" s="217"/>
-      <c r="L3" s="217"/>
-    </row>
-    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="218" t="s">
-        <v>124</v>
-      </c>
-      <c r="C4" s="218"/>
-      <c r="D4" s="218"/>
-      <c r="E4" s="218"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="218"/>
-      <c r="H4" s="218"/>
-      <c r="I4" s="218"/>
-      <c r="J4" s="218"/>
-      <c r="K4" s="218"/>
-      <c r="L4" s="218"/>
-    </row>
-    <row r="5" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="174" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="175"/>
-      <c r="D5" s="175"/>
-      <c r="E5" s="175"/>
-      <c r="F5" s="175"/>
-      <c r="G5" s="175"/>
-      <c r="H5" s="175"/>
-      <c r="I5" s="175"/>
-      <c r="J5" s="175"/>
-      <c r="K5" s="176"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="211" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="209" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="209" t="s">
-        <v>144</v>
-      </c>
-      <c r="E6" s="209" t="s">
-        <v>127</v>
-      </c>
-      <c r="F6" s="209" t="s">
-        <v>128</v>
-      </c>
-      <c r="G6" s="209" t="s">
-        <v>129</v>
-      </c>
-      <c r="H6" s="209" t="s">
-        <v>130</v>
-      </c>
-      <c r="I6" s="209" t="s">
-        <v>131</v>
-      </c>
-      <c r="J6" s="209" t="s">
-        <v>132</v>
-      </c>
-      <c r="K6" s="213" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="212"/>
-      <c r="C7" s="210"/>
-      <c r="D7" s="210"/>
-      <c r="E7" s="210"/>
-      <c r="F7" s="210"/>
-      <c r="G7" s="210"/>
-      <c r="H7" s="210"/>
-      <c r="I7" s="210"/>
-      <c r="J7" s="210"/>
-      <c r="K7" s="214"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="171">
-        <v>1</v>
-      </c>
-      <c r="C8" s="172" t="s">
-        <v>133</v>
-      </c>
-      <c r="D8" s="173">
-        <v>4901.2360000000008</v>
-      </c>
-      <c r="E8" s="173" t="s">
-        <v>134</v>
-      </c>
-      <c r="F8" s="173">
-        <v>13</v>
-      </c>
-      <c r="G8" s="133">
-        <v>45967</v>
-      </c>
-      <c r="H8" s="133">
-        <v>45968</v>
-      </c>
-      <c r="I8" s="133">
-        <v>45972</v>
-      </c>
-      <c r="J8" s="133">
-        <v>45974</v>
-      </c>
-      <c r="K8" s="203" t="s">
-        <v>135</v>
-      </c>
-      <c r="L8" s="155"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B9" s="163">
-        <v>2</v>
-      </c>
-      <c r="C9" s="164" t="s">
-        <v>136</v>
-      </c>
-      <c r="D9" s="135">
-        <v>4418.3890000000001</v>
-      </c>
-      <c r="E9" s="135" t="s">
-        <v>134</v>
-      </c>
-      <c r="F9" s="135">
-        <v>11</v>
-      </c>
-      <c r="G9" s="133">
-        <v>45977</v>
-      </c>
-      <c r="H9" s="133">
-        <v>45978</v>
-      </c>
-      <c r="I9" s="133">
-        <v>45981</v>
-      </c>
-      <c r="J9" s="133">
-        <v>45983</v>
-      </c>
-      <c r="K9" s="204"/>
-      <c r="L9" s="155"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B10" s="163">
-        <v>3</v>
-      </c>
-      <c r="C10" s="164" t="s">
-        <v>137</v>
-      </c>
-      <c r="D10" s="135">
-        <v>419.48</v>
-      </c>
-      <c r="E10" s="135" t="s">
-        <v>134</v>
-      </c>
-      <c r="F10" s="135">
-        <v>1</v>
-      </c>
-      <c r="G10" s="133">
-        <v>45984</v>
-      </c>
-      <c r="H10" s="133">
-        <v>45985</v>
-      </c>
-      <c r="I10" s="133">
-        <v>45988</v>
-      </c>
-      <c r="J10" s="133">
-        <v>45990</v>
-      </c>
-      <c r="K10" s="205"/>
-      <c r="L10" s="155"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B11" s="162">
-        <v>4</v>
-      </c>
-      <c r="C11" s="156" t="s">
-        <v>138</v>
-      </c>
-      <c r="D11" s="8">
-        <v>840.43900000000008</v>
-      </c>
-      <c r="E11" s="165" t="s">
-        <v>134</v>
-      </c>
-      <c r="F11" s="8">
-        <v>2</v>
-      </c>
-      <c r="G11" s="133">
-        <v>45971</v>
-      </c>
-      <c r="H11" s="133">
-        <v>45973</v>
-      </c>
-      <c r="I11" s="133">
-        <v>45976</v>
-      </c>
-      <c r="J11" s="133">
-        <v>45979</v>
-      </c>
-      <c r="K11" s="206" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="162">
-        <v>5</v>
-      </c>
-      <c r="C12" s="156" t="s">
-        <v>140</v>
-      </c>
-      <c r="D12" s="8">
-        <v>3283.51</v>
-      </c>
-      <c r="E12" s="165" t="s">
-        <v>134</v>
-      </c>
-      <c r="F12" s="8">
-        <v>8</v>
-      </c>
-      <c r="G12" s="133">
-        <v>45983</v>
-      </c>
-      <c r="H12" s="133">
-        <v>45984</v>
-      </c>
-      <c r="I12" s="133">
-        <v>45987</v>
-      </c>
-      <c r="J12" s="133">
-        <v>45989</v>
-      </c>
-      <c r="K12" s="207"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B13" s="162">
-        <v>6</v>
-      </c>
-      <c r="C13" s="156" t="s">
-        <v>141</v>
-      </c>
-      <c r="D13" s="8">
-        <v>4049.7639999999997</v>
-      </c>
-      <c r="E13" s="165" t="s">
-        <v>134</v>
-      </c>
-      <c r="F13" s="8">
-        <v>10</v>
-      </c>
-      <c r="G13" s="133">
-        <v>45988</v>
-      </c>
-      <c r="H13" s="133">
-        <f>G13+1</f>
-        <v>45989</v>
-      </c>
-      <c r="I13" s="133">
-        <v>45991</v>
-      </c>
-      <c r="J13" s="133">
-        <v>45995</v>
-      </c>
-      <c r="K13" s="208"/>
-    </row>
-    <row r="14" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="167"/>
-      <c r="C14" s="168"/>
-      <c r="D14" s="168"/>
-      <c r="E14" s="169"/>
-      <c r="F14" s="92"/>
-      <c r="G14" s="92"/>
-      <c r="H14" s="92"/>
-      <c r="I14" s="92"/>
-      <c r="J14" s="92"/>
-      <c r="K14" s="170"/>
-    </row>
-    <row r="15" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="158" t="s">
-        <v>142</v>
-      </c>
-      <c r="C15" s="159"/>
-      <c r="D15" s="166">
-        <v>17.912817999999998</v>
-      </c>
-      <c r="E15" s="160"/>
-      <c r="F15" s="161">
-        <v>45</v>
-      </c>
-      <c r="G15" s="161"/>
-      <c r="H15" s="161"/>
-      <c r="I15" s="161"/>
-      <c r="J15" s="161"/>
-      <c r="K15" s="157"/>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K8:K10"/>
-    <mergeCell ref="K11:K13"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="K6:K7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21CFCD75-33F5-49B3-A4C8-4F19BD2235FD}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -6635,118 +5872,118 @@
       <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="180" t="s">
+      <c r="A18" s="176" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="180" t="s">
+      <c r="B18" s="176" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="177" t="s">
+      <c r="C18" s="172" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="177" t="s">
+      <c r="D18" s="172" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="180" t="s">
+      <c r="E18" s="176" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="192" t="s">
+      <c r="F18" s="163" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="192"/>
-      <c r="H18" s="192"/>
-      <c r="I18" s="192"/>
-      <c r="J18" s="192"/>
-      <c r="K18" s="185" t="s">
+      <c r="G18" s="163"/>
+      <c r="H18" s="163"/>
+      <c r="I18" s="163"/>
+      <c r="J18" s="163"/>
+      <c r="K18" s="166" t="s">
         <v>19</v>
       </c>
-      <c r="M18" s="177" t="s">
+      <c r="M18" s="172" t="s">
         <v>36</v>
       </c>
-      <c r="O18" s="186" t="s">
+      <c r="O18" s="167" t="s">
         <v>31</v>
       </c>
-      <c r="P18" s="187"/>
-      <c r="Q18" s="187"/>
-      <c r="R18" s="187"/>
-      <c r="S18" s="187"/>
-      <c r="T18" s="188"/>
-      <c r="V18" s="186" t="s">
+      <c r="P18" s="168"/>
+      <c r="Q18" s="168"/>
+      <c r="R18" s="168"/>
+      <c r="S18" s="168"/>
+      <c r="T18" s="169"/>
+      <c r="V18" s="167" t="s">
         <v>30</v>
       </c>
-      <c r="W18" s="187"/>
-      <c r="X18" s="187"/>
-      <c r="Y18" s="187"/>
-      <c r="Z18" s="187"/>
-      <c r="AA18" s="188"/>
-      <c r="AB18" s="189" t="s">
+      <c r="W18" s="168"/>
+      <c r="X18" s="168"/>
+      <c r="Y18" s="168"/>
+      <c r="Z18" s="168"/>
+      <c r="AA18" s="169"/>
+      <c r="AB18" s="170" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:28" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="181"/>
-      <c r="B19" s="181"/>
-      <c r="C19" s="178"/>
-      <c r="D19" s="181"/>
-      <c r="E19" s="181"/>
-      <c r="F19" s="220" t="s">
+      <c r="A19" s="177"/>
+      <c r="B19" s="177"/>
+      <c r="C19" s="174"/>
+      <c r="D19" s="177"/>
+      <c r="E19" s="177"/>
+      <c r="F19" s="184" t="s">
         <v>40</v>
       </c>
-      <c r="G19" s="221" t="s">
+      <c r="G19" s="185" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="222"/>
-      <c r="I19" s="221" t="s">
+      <c r="H19" s="186"/>
+      <c r="I19" s="185" t="s">
         <v>45</v>
       </c>
-      <c r="J19" s="222"/>
-      <c r="K19" s="185"/>
-      <c r="M19" s="191"/>
-      <c r="O19" s="183" t="s">
+      <c r="J19" s="186"/>
+      <c r="K19" s="166"/>
+      <c r="M19" s="173"/>
+      <c r="O19" s="164" t="s">
         <v>24</v>
       </c>
-      <c r="P19" s="183" t="s">
+      <c r="P19" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="Q19" s="183" t="s">
+      <c r="Q19" s="164" t="s">
         <v>26</v>
       </c>
-      <c r="R19" s="183" t="s">
+      <c r="R19" s="164" t="s">
         <v>27</v>
       </c>
-      <c r="S19" s="183" t="s">
+      <c r="S19" s="164" t="s">
         <v>28</v>
       </c>
       <c r="T19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="V19" s="183" t="s">
+      <c r="V19" s="164" t="s">
         <v>24</v>
       </c>
-      <c r="W19" s="183" t="s">
+      <c r="W19" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="X19" s="183" t="s">
+      <c r="X19" s="164" t="s">
         <v>26</v>
       </c>
-      <c r="Y19" s="183" t="s">
+      <c r="Y19" s="164" t="s">
         <v>27</v>
       </c>
-      <c r="Z19" s="183" t="s">
+      <c r="Z19" s="164" t="s">
         <v>28</v>
       </c>
       <c r="AA19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AB19" s="190"/>
+      <c r="AB19" s="171"/>
     </row>
     <row r="20" spans="1:28" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="181"/>
-      <c r="B20" s="181"/>
-      <c r="C20" s="178"/>
-      <c r="D20" s="181"/>
-      <c r="E20" s="181"/>
-      <c r="F20" s="220"/>
+      <c r="A20" s="177"/>
+      <c r="B20" s="177"/>
+      <c r="C20" s="174"/>
+      <c r="D20" s="177"/>
+      <c r="E20" s="177"/>
+      <c r="F20" s="184"/>
       <c r="G20" s="93" t="s">
         <v>10</v>
       </c>
@@ -6765,17 +6002,17 @@
       <c r="M20" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="O20" s="184"/>
-      <c r="P20" s="184"/>
-      <c r="Q20" s="184"/>
-      <c r="R20" s="184"/>
-      <c r="S20" s="184"/>
+      <c r="O20" s="165"/>
+      <c r="P20" s="165"/>
+      <c r="Q20" s="165"/>
+      <c r="R20" s="165"/>
+      <c r="S20" s="165"/>
       <c r="T20" s="19"/>
-      <c r="V20" s="184"/>
-      <c r="W20" s="184"/>
-      <c r="X20" s="184"/>
-      <c r="Y20" s="184"/>
-      <c r="Z20" s="184"/>
+      <c r="V20" s="165"/>
+      <c r="W20" s="165"/>
+      <c r="X20" s="165"/>
+      <c r="Y20" s="165"/>
+      <c r="Z20" s="165"/>
       <c r="AA20" s="19" t="s">
         <v>20</v>
       </c>
@@ -6796,7 +6033,7 @@
       <c r="D21" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E21" s="219" t="s">
+      <c r="E21" s="187" t="s">
         <v>98</v>
       </c>
       <c r="F21" s="113">
@@ -6870,7 +6107,7 @@
       <c r="D22" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="219"/>
+      <c r="E22" s="187"/>
       <c r="F22" s="113">
         <v>45913</v>
       </c>
@@ -6942,7 +6179,7 @@
       <c r="D23" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="219"/>
+      <c r="E23" s="187"/>
       <c r="F23" s="113">
         <v>45910</v>
       </c>
@@ -7014,7 +6251,7 @@
       <c r="D24" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="219"/>
+      <c r="E24" s="187"/>
       <c r="F24" s="113">
         <v>45927</v>
       </c>
@@ -7086,7 +6323,7 @@
       <c r="D25" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="219"/>
+      <c r="E25" s="187"/>
       <c r="F25" s="113">
         <v>45915</v>
       </c>
@@ -7781,6 +7018,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="E21:E25"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="V18:AA18"/>
+    <mergeCell ref="V19:V20"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
     <mergeCell ref="AB18:AB19"/>
     <mergeCell ref="F19:F20"/>
     <mergeCell ref="G19:H19"/>
@@ -7794,21 +7043,9 @@
     <mergeCell ref="Q19:Q20"/>
     <mergeCell ref="R19:R20"/>
     <mergeCell ref="S19:S20"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="E21:E25"/>
-    <mergeCell ref="W19:W20"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="O18:T18"/>
-    <mergeCell ref="V18:AA18"/>
-    <mergeCell ref="V19:V20"/>
   </mergeCells>
   <conditionalFormatting sqref="C26:C27">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="4DT6">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="4DT6">
       <formula>NOT(ISERROR(SEARCH("4DT6",C26)))</formula>
     </cfRule>
   </conditionalFormatting>
